--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -21555,6 +21555,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="922">
+      <c r="A922" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B922" t="n">
+        <v>32166</v>
+      </c>
+      <c r="C922" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D922" t="n">
+        <v>3.82999992370605</v>
+      </c>
+      <c r="E922" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="F922" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G922" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -21578,6 +21578,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="923">
+      <c r="A923" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B923" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C923" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="D923" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E923" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F923" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="G923" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -21601,6 +21601,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="924">
+      <c r="A924" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B924" t="n">
+        <v>22018</v>
+      </c>
+      <c r="C924" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D924" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="E924" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="F924" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="G924" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -21624,6 +21624,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="925">
+      <c r="A925" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B925" t="n">
+        <v>33476</v>
+      </c>
+      <c r="C925" t="n">
+        <v>3.98000001907349</v>
+      </c>
+      <c r="D925" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="E925" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="F925" t="n">
+        <v>3.98000001907349</v>
+      </c>
+      <c r="G925" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -21465,19 +21465,19 @@
     </row>
     <row r="918">
       <c r="A918" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B918" t="n">
-        <v>3758</v>
+        <v>15448</v>
       </c>
       <c r="C918" t="n">
-        <v>3.82999992370605</v>
+        <v>3.80999994277954</v>
       </c>
       <c r="D918" t="n">
-        <v>3.79999995231628</v>
+        <v>3.71000003814697</v>
       </c>
       <c r="E918" t="n">
-        <v>3.82999992370605</v>
+        <v>3.77999997138977</v>
       </c>
       <c r="F918" t="n">
         <v>3.79999995231628</v>
@@ -21488,22 +21488,22 @@
     </row>
     <row r="919">
       <c r="A919" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B919" t="n">
-        <v>17880</v>
+        <v>3758</v>
       </c>
       <c r="C919" t="n">
-        <v>3.85999989509583</v>
+        <v>3.82999992370605</v>
       </c>
       <c r="D919" t="n">
-        <v>3.70000004768372</v>
+        <v>3.79999995231628</v>
       </c>
       <c r="E919" t="n">
-        <v>3.83999991416931</v>
+        <v>3.82999992370605</v>
       </c>
       <c r="F919" t="n">
-        <v>3.85999989509583</v>
+        <v>3.79999995231628</v>
       </c>
       <c r="G919" t="s">
         <v>7</v>
@@ -21511,22 +21511,22 @@
     </row>
     <row r="920">
       <c r="A920" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B920" t="n">
-        <v>35164</v>
+        <v>17880</v>
       </c>
       <c r="C920" t="n">
-        <v>3.92000007629395</v>
+        <v>3.85999989509583</v>
       </c>
       <c r="D920" t="n">
-        <v>3.79999995231628</v>
+        <v>3.70000004768372</v>
       </c>
       <c r="E920" t="n">
-        <v>3.86999988555908</v>
+        <v>3.83999991416931</v>
       </c>
       <c r="F920" t="n">
-        <v>3.91000008583069</v>
+        <v>3.85999989509583</v>
       </c>
       <c r="G920" t="s">
         <v>7</v>
@@ -21534,22 +21534,22 @@
     </row>
     <row r="921">
       <c r="A921" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B921" t="n">
-        <v>8315</v>
+        <v>35164</v>
       </c>
       <c r="C921" t="n">
-        <v>3.95000004768372</v>
+        <v>3.92000007629395</v>
       </c>
       <c r="D921" t="n">
-        <v>3.90000009536743</v>
+        <v>3.79999995231628</v>
       </c>
       <c r="E921" t="n">
-        <v>3.94000005722046</v>
+        <v>3.86999988555908</v>
       </c>
       <c r="F921" t="n">
-        <v>3.9300000667572</v>
+        <v>3.91000008583069</v>
       </c>
       <c r="G921" t="s">
         <v>7</v>
@@ -21557,16 +21557,16 @@
     </row>
     <row r="922">
       <c r="A922" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B922" t="n">
-        <v>32166</v>
+        <v>8315</v>
       </c>
       <c r="C922" t="n">
-        <v>3.96000003814697</v>
+        <v>3.95000004768372</v>
       </c>
       <c r="D922" t="n">
-        <v>3.82999992370605</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="E922" t="n">
         <v>3.94000005722046</v>
@@ -21580,22 +21580,22 @@
     </row>
     <row r="923">
       <c r="A923" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B923" t="n">
-        <v>2245</v>
+        <v>32166</v>
       </c>
       <c r="C923" t="n">
-        <v>3.95000004768372</v>
+        <v>3.96000003814697</v>
       </c>
       <c r="D923" t="n">
-        <v>3.90000009536743</v>
+        <v>3.82999992370605</v>
       </c>
       <c r="E923" t="n">
-        <v>3.90000009536743</v>
+        <v>3.94000005722046</v>
       </c>
       <c r="F923" t="n">
-        <v>3.95000004768372</v>
+        <v>3.9300000667572</v>
       </c>
       <c r="G923" t="s">
         <v>7</v>
@@ -21603,19 +21603,19 @@
     </row>
     <row r="924">
       <c r="A924" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B924" t="n">
-        <v>22018</v>
+        <v>2245</v>
       </c>
       <c r="C924" t="n">
-        <v>3.96000003814697</v>
+        <v>3.95000004768372</v>
       </c>
       <c r="D924" t="n">
-        <v>3.92000007629395</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="E924" t="n">
-        <v>3.94000005722046</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="F924" t="n">
         <v>3.95000004768372</v>
@@ -21626,24 +21626,47 @@
     </row>
     <row r="925">
       <c r="A925" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B925" t="n">
-        <v>33476</v>
+        <v>22018</v>
       </c>
       <c r="C925" t="n">
-        <v>3.98000001907349</v>
+        <v>3.96000003814697</v>
       </c>
       <c r="D925" t="n">
-        <v>3.94000005722046</v>
+        <v>3.92000007629395</v>
       </c>
       <c r="E925" t="n">
         <v>3.94000005722046</v>
       </c>
       <c r="F925" t="n">
-        <v>3.98000001907349</v>
+        <v>3.95000004768372</v>
       </c>
       <c r="G925" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B926" t="n">
+        <v>82939</v>
+      </c>
+      <c r="C926" t="n">
+        <v>4.05999994277954</v>
+      </c>
+      <c r="D926" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="E926" t="n">
+        <v>3.99000000953674</v>
+      </c>
+      <c r="F926" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="G926" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -24503,6 +24503,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="929">
+      <c r="A929" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B929" t="n">
+        <v>29143</v>
+      </c>
+      <c r="C929" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="D929" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="E929" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="F929" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="G929" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="H929" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -24529,6 +24529,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="930">
+      <c r="A930" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B930" t="n">
+        <v>2722</v>
+      </c>
+      <c r="C930" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="D930" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="E930" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="F930" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="G930" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="H930" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -24555,6 +24555,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="931">
+      <c r="A931" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B931" t="n">
+        <v>3590</v>
+      </c>
+      <c r="C931" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D931" t="n">
+        <v>3.89000010490417</v>
+      </c>
+      <c r="E931" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F931" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="G931" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="H931" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -24581,6 +24581,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="932">
+      <c r="A932" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B932" t="n">
+        <v>23619</v>
+      </c>
+      <c r="C932" t="n">
+        <v>3.99000000953674</v>
+      </c>
+      <c r="D932" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E932" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="F932" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="G932" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="H932" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -24659,6 +24659,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="935">
+      <c r="A935" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B935" t="n">
+        <v>16994</v>
+      </c>
+      <c r="C935" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="D935" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="E935" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F935" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="G935" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="H935" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -21939,8 +21939,31 @@
       <c r="E938" t="n">
         <v>3.90000009536743</v>
       </c>
-      <c r="F938"/>
+      <c r="F938" t="n">
+        <v>3.91000008583069</v>
+      </c>
       <c r="G938" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B939" t="n">
+        <v>14731</v>
+      </c>
+      <c r="C939" t="n">
+        <v>4</v>
+      </c>
+      <c r="D939" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E939" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="F939"/>
+      <c r="G939" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -21962,8 +21962,31 @@
       <c r="E939" t="n">
         <v>3.9300000667572</v>
       </c>
-      <c r="F939"/>
+      <c r="F939" t="n">
+        <v>3.94000005722046</v>
+      </c>
       <c r="G939" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B940" t="n">
+        <v>14663</v>
+      </c>
+      <c r="C940" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="D940" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="E940" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F940"/>
+      <c r="G940" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -21985,8 +21985,31 @@
       <c r="E940" t="n">
         <v>3.90000009536743</v>
       </c>
-      <c r="F940"/>
+      <c r="F940" t="n">
+        <v>3.79999995231628</v>
+      </c>
       <c r="G940" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B941" t="n">
+        <v>14802</v>
+      </c>
+      <c r="C941" t="n">
+        <v>3.9300000667572</v>
+      </c>
+      <c r="D941" t="n">
+        <v>3.82999992370605</v>
+      </c>
+      <c r="E941" t="n">
+        <v>3.84999990463257</v>
+      </c>
+      <c r="F941"/>
+      <c r="G941" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -22008,8 +22008,31 @@
       <c r="E941" t="n">
         <v>3.84999990463257</v>
       </c>
-      <c r="F941"/>
+      <c r="F941" t="n">
+        <v>3.92000007629395</v>
+      </c>
       <c r="G941" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B942" t="n">
+        <v>10675</v>
+      </c>
+      <c r="C942" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="D942" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="E942" t="n">
+        <v>3.86999988555908</v>
+      </c>
+      <c r="F942"/>
+      <c r="G942" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -22038,6 +22038,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="943">
+      <c r="A943" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B943" t="n">
+        <v>7971</v>
+      </c>
+      <c r="C943" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="D943" t="n">
+        <v>3.82999992370605</v>
+      </c>
+      <c r="E943" t="n">
+        <v>3.91000008583069</v>
+      </c>
+      <c r="F943" t="n">
+        <v>3.86999988555908</v>
+      </c>
+      <c r="G943" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -24945,6 +24945,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="946">
+      <c r="A946" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B946" t="n">
+        <v>17619</v>
+      </c>
+      <c r="C946" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="D946" t="n">
+        <v>3.71000003814697</v>
+      </c>
+      <c r="E946" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="F946" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="G946" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="H946" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -24971,6 +24971,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B947" t="n">
+        <v>15944</v>
+      </c>
+      <c r="C947" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D947" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E947" t="n">
+        <v>3.69000005722046</v>
+      </c>
+      <c r="F947" t="n">
+        <v>3.63000011444092</v>
+      </c>
+      <c r="G947" t="n">
+        <v>3.63000011444092</v>
+      </c>
+      <c r="H947" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -27841,6 +27841,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" t="s">
+        <v>9</v>
+      </c>
+      <c r="B948" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C948" t="n">
+        <v>3.63000011444092</v>
+      </c>
+      <c r="D948" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E948" t="n">
+        <v>3.63000011444092</v>
+      </c>
+      <c r="F948" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="G948" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="H948" t="n">
+        <v>21905</v>
+      </c>
+      <c r="I948" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="s">
+        <v>9</v>
+      </c>
+      <c r="B949" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C949" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="D949" t="n">
+        <v>3.78999996185303</v>
+      </c>
+      <c r="E949" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F949" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="G949" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="H949" t="n">
+        <v>26054</v>
+      </c>
+      <c r="I949" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -27899,6 +27899,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" t="s">
+        <v>9</v>
+      </c>
+      <c r="B950" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C950" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="D950" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="E950" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F950" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="G950" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="H950" t="n">
+        <v>19417</v>
+      </c>
+      <c r="I950" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -27928,6 +27928,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" t="s">
+        <v>9</v>
+      </c>
+      <c r="B951" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C951" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="D951" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="E951" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="F951" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G951" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H951" t="n">
+        <v>64291</v>
+      </c>
+      <c r="I951" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -27957,6 +27957,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" t="s">
+        <v>9</v>
+      </c>
+      <c r="B952" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C952" t="n">
+        <v>3.63000011444092</v>
+      </c>
+      <c r="D952" t="n">
+        <v>3.63000011444092</v>
+      </c>
+      <c r="E952" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="F952" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G952" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H952" t="n">
+        <v>7558</v>
+      </c>
+      <c r="I952" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -27986,6 +27986,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="953">
+      <c r="A953" t="s">
+        <v>9</v>
+      </c>
+      <c r="B953" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C953" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="D953" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="E953" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="F953" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="G953" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="H953" t="n">
+        <v>15429</v>
+      </c>
+      <c r="I953" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -28015,6 +28015,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="954">
+      <c r="A954" t="s">
+        <v>9</v>
+      </c>
+      <c r="B954" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C954" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="D954" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="E954" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="F954" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G954" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="H954" t="n">
+        <v>1455</v>
+      </c>
+      <c r="I954" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -28044,6 +28044,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" t="s">
+        <v>9</v>
+      </c>
+      <c r="B955" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C955" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D955" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="E955" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F955" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G955" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H955" t="n">
+        <v>14355</v>
+      </c>
+      <c r="I955" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -28073,6 +28073,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="956">
+      <c r="A956" t="s">
+        <v>9</v>
+      </c>
+      <c r="B956" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C956" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="D956" t="n">
+        <v>3.66000008583069</v>
+      </c>
+      <c r="E956" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F956" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G956" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="H956" t="n">
+        <v>35154</v>
+      </c>
+      <c r="I956" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FAE.MI.xlsx
+++ b/data/FAE.MI.xlsx
@@ -28102,6 +28102,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="957">
+      <c r="A957" t="s">
+        <v>9</v>
+      </c>
+      <c r="B957" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C957" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="D957" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="E957" t="n">
+        <v>3.47000002861023</v>
+      </c>
+      <c r="F957" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="G957" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="H957" t="n">
+        <v>12680</v>
+      </c>
+      <c r="I957" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
